--- a/簡単なサービス請求書1.xlsx
+++ b/簡単なサービス請求書1.xlsx
@@ -3,16 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2768DCD9-F909-49A4-90AD-0441AA7563BB}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF48C701-957C-4AE0-9CDF-6E40D830F439}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="24" r:id="rId1"/>
     <sheet name="データ取り込み" sheetId="26" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">請求書!$A$1:$H$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">請求書!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
   <si>
     <t>[会社名]</t>
   </si>
@@ -62,12 +62,6 @@
     <t>説明</t>
   </si>
   <si>
-    <t>サービス料</t>
-  </si>
-  <si>
-    <t>新規顧客の割引額</t>
-  </si>
-  <si>
     <t>ご利用ありがとうございます。</t>
   </si>
   <si>
@@ -149,47 +143,47 @@
     <t>← この情報を更新するか、この 2 行を削除してください。</t>
   </si>
   <si>
-    <t>人件費:5 時間 (¥75/1 時間)</t>
+    <t>取引先名</t>
+  </si>
+  <si>
+    <t>請求番号</t>
+  </si>
+  <si>
+    <t>発行日</t>
+  </si>
+  <si>
+    <t>支払期限</t>
+  </si>
+  <si>
+    <t>請求金額</t>
+  </si>
+  <si>
+    <t>税区分</t>
+  </si>
+  <si>
+    <t>件名</t>
+  </si>
+  <si>
+    <t>明細</t>
+  </si>
+  <si>
+    <t>株式会社サンプル</t>
+  </si>
+  <si>
+    <t>INV-2026-0331</t>
+  </si>
+  <si>
+    <t>会計ソフトつくった</t>
+  </si>
+  <si>
+    <t>いっぱいがんばった</t>
+  </si>
+  <si>
+    <t>件名：</t>
+    <rPh sb="0" eb="2">
+      <t>ケンメイ</t>
+    </rPh>
     <phoneticPr fontId="24"/>
-  </si>
-  <si>
-    <t>取引先名</t>
-  </si>
-  <si>
-    <t>請求番号</t>
-  </si>
-  <si>
-    <t>発行日</t>
-  </si>
-  <si>
-    <t>支払期限</t>
-  </si>
-  <si>
-    <t>請求金額</t>
-  </si>
-  <si>
-    <t>税区分</t>
-  </si>
-  <si>
-    <t>件名</t>
-  </si>
-  <si>
-    <t>明細</t>
-  </si>
-  <si>
-    <t>株式会社サンプル</t>
-  </si>
-  <si>
-    <t>INV-2026-0331</t>
-  </si>
-  <si>
-    <t>課税 10%</t>
-  </si>
-  <si>
-    <t>会計ソフトつくった</t>
-  </si>
-  <si>
-    <t>いっぱいがんばった</t>
   </si>
 </sst>
 </file>
@@ -474,7 +468,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,18 +585,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -722,41 +710,6 @@
       <right style="hair">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -837,15 +790,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="hair">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="hair">
         <color auto="1"/>
       </top>
@@ -921,7 +865,7 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -976,19 +920,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1000,22 +948,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1039,11 +971,11 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="22" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="23" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1053,13 +985,6 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="34" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1082,7 +1007,7 @@
     <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1098,6 +1023,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1559,12 +1487,12 @@
   <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.77734375" style="3" customWidth="1"/>
     <col min="4" max="6" width="6.77734375" style="3" customWidth="1"/>
     <col min="7" max="7" width="12.77734375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" style="3" customWidth="1"/>
     <col min="10" max="10" width="29.109375" style="3" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="3"/>
@@ -1579,21 +1507,24 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="G1" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="45"/>
-    </row>
-    <row r="2" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
+      <c r="G1" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="40"/>
+    </row>
+    <row r="2" spans="1:11" ht="43.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="5" t="str">
+        <f>データ取り込み!$G$2</f>
+        <v>会計ソフトつくった</v>
+      </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
       <c r="J2" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K2" s="9"/>
     </row>
@@ -1606,7 +1537,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
       <c r="J3" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K3" s="10"/>
     </row>
@@ -1618,12 +1549,12 @@
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="47"/>
+      <c r="F4" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="42"/>
       <c r="H4" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J4" s="12"/>
     </row>
@@ -1633,11 +1564,11 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="48" t="str">
+      <c r="F5" s="43" t="str">
         <f>データ取り込み!$B$2</f>
         <v>INV-2026-0331</v>
       </c>
-      <c r="G5" s="48"/>
+      <c r="G5" s="43"/>
       <c r="H5" s="13">
         <f>データ取り込み!$C$2</f>
         <v>46086</v>
@@ -1656,22 +1587,22 @@
       <c r="J6" s="14"/>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
       <c r="D7" s="7"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="47"/>
+      <c r="F7" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="42"/>
       <c r="H7" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1682,10 +1613,10 @@
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="49">
+      <c r="F8" s="44">
         <v>564</v>
       </c>
-      <c r="G8" s="49"/>
+      <c r="G8" s="44"/>
       <c r="H8" s="13">
         <f>データ取り込み!$D$2</f>
         <v>46117</v>
@@ -1730,7 +1661,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="J11" s="16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1745,7 +1676,7 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="J12" s="12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
@@ -1760,7 +1691,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="J13" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -1773,7 +1704,7 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="J14" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
@@ -1785,381 +1716,333 @@
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="19" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="19"/>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
       <c r="E16" s="20"/>
-      <c r="F16" s="21">
-        <v>1</v>
-      </c>
-      <c r="G16" s="38">
-        <v>200</v>
-      </c>
-      <c r="H16" s="39">
-        <f>IF(F16="",ROUND(1*G16,2),ROUND(F16*G16,2))</f>
-        <v>200</v>
+      <c r="F16" s="22"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36">
+        <f t="shared" ref="H16:H27" si="0">IF(F16="",ROUND(1*G16,2),ROUND(F16*G16,2))</f>
+        <v>0</v>
       </c>
       <c r="J16" s="12"/>
     </row>
     <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="24">
-        <v>5</v>
-      </c>
-      <c r="G17" s="40">
-        <v>75</v>
-      </c>
-      <c r="H17" s="41">
-        <f t="shared" ref="H17:H30" si="0">IF(F17="",ROUND(1*G17,2),ROUND(F17*G17,2))</f>
-        <v>375</v>
-      </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="40">
-        <v>-50</v>
-      </c>
-      <c r="H18" s="41">
-        <f t="shared" si="0"/>
-        <v>-50</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="22"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="41">
+      <c r="J17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="22"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41">
+      <c r="J18" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="41">
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41">
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41">
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36">
+        <f t="shared" ref="H22" si="1">IF(F22="",ROUND(1*G22,2),ROUND(F22*G22,2))</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41">
-        <f t="shared" ref="H25" si="1">IF(F25="",ROUND(1*G25,2),ROUND(F25*G25,2))</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41">
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41">
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41">
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="22"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41">
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="47"/>
+      <c r="H28" s="39">
+        <f>データ取り込み!$E$2</f>
+        <v>20000000</v>
+      </c>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="47"/>
+      <c r="H29" s="30">
+        <f>データ取り込み!$F$2</f>
+        <v>0.1</v>
+      </c>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="26"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43">
-        <f t="shared" si="0"/>
-        <v>0</v>
+    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="26"/>
+      <c r="H30" s="39">
+        <f>H28*H29</f>
+        <v>2000000</v>
       </c>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="1:10" s="30" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="51" t="s">
+    <row r="31" spans="1:10" s="27" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32">
+        <f>H28+H30</f>
+        <v>22000000</v>
+      </c>
+      <c r="J31" s="12"/>
+    </row>
+    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="6"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="J32" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="J34" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A35" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="51"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="52"/>
-      <c r="H31" s="44">
-        <f>SUM(H16:H30)</f>
-        <v>525</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A32" s="31"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="G32" s="52"/>
-      <c r="H32" s="33">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="J32" s="12" t="s">
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="41"/>
+      <c r="H35" s="41"/>
+      <c r="J35" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A33" s="31"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="44">
-        <f>H31*H32</f>
-        <v>22.3125</v>
-      </c>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A34" s="31"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="34"/>
-      <c r="H34" s="35">
-        <f>H31+H33</f>
-        <v>547.3125</v>
-      </c>
-      <c r="J34" s="12" t="s">
+    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J36" s="12"/>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J37" s="18"/>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J38" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A35" s="6"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="J35" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="J36" s="12"/>
-    </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
-      <c r="J37" s="18"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="46"/>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
-      <c r="E38" s="46"/>
-      <c r="F38" s="46"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="46"/>
-      <c r="J38" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="J39" s="37"/>
+      <c r="J39" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <phoneticPr fontId="24"/>
   <dataValidations disablePrompts="1" count="1">
@@ -2187,55 +2070,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="E1" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="F1" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="G1" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="H1" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="54" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="B2" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="C2" s="50">
+        <v>46086</v>
+      </c>
+      <c r="D2" s="50">
+        <v>46117</v>
+      </c>
+      <c r="E2" s="51">
+        <v>20000000</v>
+      </c>
+      <c r="F2" s="52">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="49" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="54" t="s">
+      <c r="H2" s="49" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="55">
-        <v>46086</v>
-      </c>
-      <c r="D2" s="55">
-        <v>46117</v>
-      </c>
-      <c r="E2" s="56">
-        <v>20000000</v>
-      </c>
-      <c r="F2" s="54" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="54" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/簡単なサービス請求書1.xlsx
+++ b/簡単なサービス請求書1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF48C701-957C-4AE0-9CDF-6E40D830F439}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F37E08-7401-49A7-80DA-A10092A8713D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>[会社名]</t>
   </si>
@@ -44,9 +44,6 @@
     <t>[郵便番号、都道府県]</t>
   </si>
   <si>
-    <t>電話:(000) 000-0000</t>
-  </si>
-  <si>
     <t>請求先</t>
   </si>
   <si>
@@ -141,47 +138,18 @@
   </si>
   <si>
     <t>← この情報を更新するか、この 2 行を削除してください。</t>
-  </si>
-  <si>
-    <t>取引先名</t>
-  </si>
-  <si>
-    <t>請求番号</t>
-  </si>
-  <si>
-    <t>発行日</t>
-  </si>
-  <si>
-    <t>支払期限</t>
-  </si>
-  <si>
-    <t>請求金額</t>
-  </si>
-  <si>
-    <t>税区分</t>
-  </si>
-  <si>
-    <t>件名</t>
-  </si>
-  <si>
-    <t>明細</t>
-  </si>
-  <si>
-    <t>株式会社サンプル</t>
-  </si>
-  <si>
-    <t>INV-2026-0331</t>
-  </si>
-  <si>
-    <t>会計ソフトつくった</t>
-  </si>
-  <si>
-    <t>いっぱいがんばった</t>
   </si>
   <si>
     <t>件名：</t>
     <rPh sb="0" eb="2">
       <t>ケンメイ</t>
+    </rPh>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>詳細：</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
     </rPh>
     <phoneticPr fontId="24"/>
   </si>
@@ -1499,62 +1467,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="str">
+      <c r="A1" s="1">
         <f>データ取り込み!$A$2</f>
-        <v>株式会社サンプル</v>
+        <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="G1" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:11" ht="43.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="5" t="str">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1">
         <f>データ取り込み!$G$2</f>
-        <v>会計ソフトつくった</v>
+        <v>0</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
       <c r="J2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
+      <c r="A3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1">
+        <f>データ取り込み!$H$2</f>
+        <v>0</v>
+      </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
       <c r="J3" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
+      <c r="A4" s="4"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
       <c r="F4" s="42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" s="42"/>
       <c r="H4" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J4" s="12"/>
     </row>
@@ -1564,14 +1533,14 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="43" t="str">
+      <c r="F5" s="43">
         <f>データ取り込み!$B$2</f>
-        <v>INV-2026-0331</v>
+        <v>0</v>
       </c>
       <c r="G5" s="43"/>
       <c r="H5" s="13">
         <f>データ取り込み!$C$2</f>
-        <v>46086</v>
+        <v>0</v>
       </c>
       <c r="J5" s="12"/>
     </row>
@@ -1588,26 +1557,26 @@
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="45"/>
       <c r="C7" s="45"/>
       <c r="D7" s="7"/>
       <c r="E7" s="14"/>
       <c r="F7" s="42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" s="42"/>
       <c r="H7" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -1619,7 +1588,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="13">
         <f>データ取り込み!$D$2</f>
-        <v>46117</v>
+        <v>0</v>
       </c>
       <c r="J8" s="12"/>
     </row>
@@ -1661,12 +1630,12 @@
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
       <c r="J11" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -1676,12 +1645,12 @@
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
       <c r="J12" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1691,7 +1660,7 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="J13" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -1704,25 +1673,25 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="J14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15" s="18"/>
     </row>
@@ -1767,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1898,19 +1867,19 @@
     </row>
     <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="46"/>
       <c r="C28" s="46"/>
       <c r="D28" s="46"/>
       <c r="E28" s="46"/>
       <c r="F28" s="47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="39">
         <f>データ取り込み!$E$2</f>
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="J28" s="18"/>
     </row>
@@ -1921,12 +1890,12 @@
       <c r="D29" s="29"/>
       <c r="E29" s="29"/>
       <c r="F29" s="47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="47"/>
       <c r="H29" s="30">
         <f>データ取り込み!$F$2</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="18"/>
     </row>
@@ -1937,12 +1906,12 @@
       <c r="D30" s="29"/>
       <c r="E30" s="29"/>
       <c r="F30" s="26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" s="26"/>
       <c r="H30" s="39">
         <f>H28*H29</f>
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="J30" s="18"/>
     </row>
@@ -1953,12 +1922,12 @@
       <c r="D31" s="29"/>
       <c r="E31" s="29"/>
       <c r="F31" s="31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G31" s="31"/>
       <c r="H31" s="32">
         <f>H28+H30</f>
-        <v>22000000</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12"/>
     </row>
@@ -1972,7 +1941,7 @@
       <c r="G32" s="33"/>
       <c r="H32" s="33"/>
       <c r="J32" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -1988,7 +1957,7 @@
     </row>
     <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" s="48"/>
       <c r="C34" s="48"/>
@@ -1998,12 +1967,12 @@
       <c r="G34" s="48"/>
       <c r="H34" s="48"/>
       <c r="J34" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A35" s="41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
@@ -2013,7 +1982,7 @@
       <c r="G35" s="41"/>
       <c r="H35" s="41"/>
       <c r="J35" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2024,7 +1993,7 @@
     </row>
     <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="J38" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.45">
@@ -2070,56 +2039,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="49" t="s">
-        <v>43</v>
-      </c>
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="50">
-        <v>46086</v>
-      </c>
-      <c r="D2" s="50">
-        <v>46117</v>
-      </c>
-      <c r="E2" s="51">
-        <v>20000000</v>
-      </c>
-      <c r="F2" s="52">
-        <v>0.1</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>47</v>
-      </c>
+      <c r="A2" s="49"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24"/>

--- a/簡単なサービス請求書1.xlsx
+++ b/簡単なサービス請求書1.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09F37E08-7401-49A7-80DA-A10092A8713D}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{5FC131FE-3DCB-44F8-A694-2E3C6926BBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93348C9D-C67E-4261-8822-F1AD2AD27429}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="請求書" sheetId="24" r:id="rId1"/>
-    <sheet name="データ取り込み" sheetId="26" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="27" r:id="rId2"/>
+    <sheet name="データ取り込み" sheetId="26" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">請求書!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">請求書!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -104,40 +105,40 @@
     <t>金額</t>
   </si>
   <si>
-    <t>Vertex42.com による請求書テンプレート</t>
-  </si>
-  <si>
-    <t>https://www.vertex42.com/ExcelTemplates/invoice-templates.html</t>
-  </si>
-  <si>
-    <t>← "支払条件" を "支払い期日" に変更して、日付を入力することができます (通常は、請求日の 30 日後)</t>
-  </si>
-  <si>
-    <t>顧客への請求書の送付方法</t>
-  </si>
-  <si>
-    <t>1) ワークシートを PDF で保存および印刷します</t>
-  </si>
-  <si>
-    <t>2) 記録のために請求書のコピーを保存します</t>
-  </si>
-  <si>
-    <t>3) PDF を電子メールで顧客に送ります</t>
-  </si>
-  <si>
-    <t>← "数量" を空白のままとした場合、数量は 1 と見なされます</t>
-  </si>
-  <si>
-    <t>← 適切な税率を入力します</t>
-  </si>
-  <si>
-    <t>← セルの書式設定を編集して通貨を変更します</t>
-  </si>
-  <si>
-    <t>← これが受領書である場合は、"全額お支払いいただきました。ありがとうございます" などのメモを入力します</t>
-  </si>
-  <si>
-    <t>← この情報を更新するか、この 2 行を削除してください。</t>
+    <t>取引先名</t>
+  </si>
+  <si>
+    <t>請求番号</t>
+  </si>
+  <si>
+    <t>発行日</t>
+  </si>
+  <si>
+    <t>支払期限</t>
+  </si>
+  <si>
+    <t>請求金額</t>
+  </si>
+  <si>
+    <t>税区分</t>
+  </si>
+  <si>
+    <t>件名</t>
+  </si>
+  <si>
+    <t>明細</t>
+  </si>
+  <si>
+    <t>株式会社サンプル</t>
+  </si>
+  <si>
+    <t>INV-2026-0331</t>
+  </si>
+  <si>
+    <t>会計ソフトつくった</t>
+  </si>
+  <si>
+    <t>いっぱいがんばった</t>
   </si>
   <si>
     <t>件名：</t>
@@ -166,7 +167,7 @@
     <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Meiryo UI"/>
@@ -363,29 +364,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Meiryo UI"/>
@@ -416,13 +394,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.34998626667073579"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -833,7 +804,7 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -859,35 +830,19 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -900,10 +855,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -916,29 +867,28 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="34" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="178" fontId="31" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="44" fontId="36" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="33" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -953,7 +903,7 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="34" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="31" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -962,7 +912,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -972,13 +922,13 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1140,8 +1090,8 @@
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1640417</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>71594</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>492919</xdr:rowOff>
     </xdr:to>
@@ -1452,7 +1402,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3" customWidth="1"/>
@@ -1462,89 +1412,78 @@
     <col min="7" max="7" width="12.77734375" style="3" customWidth="1"/>
     <col min="8" max="8" width="20.109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="11.77734375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="29.109375" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="3"/>
+    <col min="10" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1">
+    <row r="1" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="str">
         <f>データ取り込み!$A$2</f>
-        <v>0</v>
+        <v>株式会社サンプル</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="40"/>
-    </row>
-    <row r="2" spans="1:11" ht="43.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:8" ht="43.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="1" t="str">
         <f>データ取り込み!$G$2</f>
-        <v>0</v>
+        <v>会計ソフトつくった</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
-      <c r="J2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="9"/>
-    </row>
-    <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="1" t="str">
         <f>データ取り込み!$H$2</f>
-        <v>0</v>
+        <v>いっぱいがんばった</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="7"/>
-      <c r="J3" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="10"/>
-    </row>
-    <row r="4" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="11" t="s">
+      <c r="G4" s="34"/>
+      <c r="H4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="43">
+      <c r="F5" s="35" t="str">
         <f>データ取り込み!$B$2</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="43"/>
-      <c r="H5" s="13">
+        <v>INV-2026-0331</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="9">
         <f>データ取り込み!$C$2</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="12"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -1553,102 +1492,89 @@
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
-      <c r="J6" s="14"/>
-    </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="45" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="42" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="11" t="s">
+      <c r="G7" s="34"/>
+      <c r="H7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="44">
+      <c r="E8" s="10"/>
+      <c r="F8" s="36">
         <v>564</v>
       </c>
-      <c r="G8" s="44"/>
-      <c r="H8" s="13">
+      <c r="G8" s="36"/>
+      <c r="H8" s="9">
         <f>データ取り込み!$D$2</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="14"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
-      <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="J10" s="14"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="14"/>
+      <c r="E11" s="10"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
-      <c r="J11" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="14"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
-      <c r="J12" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
@@ -1659,11 +1585,8 @@
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
-      <c r="J13" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -1672,365 +1595,230 @@
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
-      <c r="J14" s="12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="15" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="18"/>
-    </row>
-    <row r="16" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36">
-        <f t="shared" ref="H16:H27" si="0">IF(F16="",ROUND(1*G16,2),ROUND(F16*G16,2))</f>
+    </row>
+    <row r="16" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="28">
+        <f t="shared" ref="H16:H19" si="0">IF(F16="",ROUND(1*G16,2),ROUND(F16*G16,2))</f>
         <v>0</v>
       </c>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36">
+    </row>
+    <row r="17" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="19"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36">
+    </row>
+    <row r="18" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="28">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="36">
+    </row>
+    <row r="19" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J19" s="18"/>
-    </row>
-    <row r="20" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="18"/>
-    </row>
-    <row r="21" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="18"/>
-    </row>
-    <row r="22" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="36">
-        <f t="shared" ref="H22" si="1">IF(F22="",ROUND(1*G22,2),ROUND(F22*G22,2))</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="18"/>
-    </row>
-    <row r="23" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="18"/>
-    </row>
-    <row r="24" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="18"/>
-    </row>
-    <row r="25" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="18"/>
-    </row>
-    <row r="26" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="18"/>
-    </row>
-    <row r="27" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="18"/>
-    </row>
-    <row r="28" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="46" t="s">
+    </row>
+    <row r="20" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="47" t="s">
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="47"/>
-      <c r="H28" s="39">
+      <c r="G20" s="39"/>
+      <c r="H20" s="31">
         <f>データ取り込み!$E$2</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="18"/>
-    </row>
-    <row r="29" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="47" t="s">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="G29" s="47"/>
-      <c r="H29" s="30">
+      <c r="G21" s="39"/>
+      <c r="H21" s="23">
         <f>データ取り込み!$F$2</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="18"/>
-    </row>
-    <row r="30" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="26" t="s">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="39">
-        <f>H28*H29</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="18"/>
-    </row>
-    <row r="31" spans="1:10" s="27" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="31" t="s">
+      <c r="G22" s="19"/>
+      <c r="H22" s="31">
+        <f>H20*H21</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="20" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="32">
-        <f>H28+H30</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="6"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="J32" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="48" t="s">
+      <c r="G23" s="24"/>
+      <c r="H23" s="25">
+        <f>Sheet2!$A$2</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="6"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+    </row>
+    <row r="25" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="J34" s="12" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A35" s="41" t="s">
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="J35" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J36" s="12"/>
-    </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J37" s="18"/>
-    </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J38" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="J39" s="34"/>
-    </row>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+    </row>
+    <row r="28" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="30" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A26:H26"/>
   </mergeCells>
   <phoneticPr fontId="24"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:H1" xr:uid="{A6F7FD24-14BC-406B-9AFB-0EB1E3040929}">
       <formula1>"請求書,領収書"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.25"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFECBD18-7AAF-4117-9B4B-194C7B1FED96}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="24"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D587EEE-9C11-4B75-8D23-1E095C4235B7}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.45"/>
@@ -2039,24 +1827,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
+      <c r="A1" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="49"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+      <c r="A2" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="42">
+        <v>46086</v>
+      </c>
+      <c r="D2" s="42">
+        <v>46117</v>
+      </c>
+      <c r="E2" s="43">
+        <v>20000000</v>
+      </c>
+      <c r="F2" s="44">
+        <v>0.1</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="41" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="24"/>
